--- a/AIVIA_Design/L1_Code_Structure_Map_DRAFT.xlsx
+++ b/AIVIA_Design/L1_Code_Structure_Map_DRAFT.xlsx
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -930,7 +930,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>INTAKE-0..7; LC-F5 atomicity decided BEFORE any write</t>
+          <t>INTAKE-0..9 (8: unregistered db refused; 9: declared-vs-captured agreement); LC-F5 atomicity decided BEFORE any write</t>
         </is>
       </c>
     </row>
@@ -1390,6 +1390,33 @@
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>the ONLY import surface for Level 2 (plank); B3 on every result</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>kg1_intake.apply_registration</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>RegistrationPrereq (DBA-completed: db, server, dba team, sources)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>db node + layer-3 dba responsibility</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>KG1 db mint + LC3-C (responsibility)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>A1 refined: runs BEFORE any extract intake; the only path that mints a db node</t>
         </is>
       </c>
     </row>

--- a/AIVIA_Design/L1_Code_Structure_Map_DRAFT.xlsx
+++ b/AIVIA_Design/L1_Code_Structure_Map_DRAFT.xlsx
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>RegistrationPrereq (DBA-completed: db, server, dba team, sources)</t>
+          <t>RegistrationPrereq (DBA-completed: db, server, dba team, sources, schema-&gt;source mapping)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>A1 refined: runs BEFORE any extract intake; the only path that mints a db node</t>
+          <t>A1 refined + source ruling: runs BEFORE any intake; the only path that mints a db node; the mapping is where source identities originate</t>
         </is>
       </c>
     </row>

--- a/AIVIA_Design/L1_Code_Structure_Map_DRAFT.xlsx
+++ b/AIVIA_Design/L1_Code_Structure_Map_DRAFT.xlsx
@@ -930,7 +930,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>INTAKE-0..9 (8: unregistered db refused; 9: declared-vs-captured agreement); LC-F5 atomicity decided BEFORE any write</t>
+          <t>INTAKE-0..10 (8 unregistered db; 9 declared-vs-captured; 10 pk integrity); LC-F5 atomicity decided BEFORE any write</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>business_name? grain? pk_columns? + gap rows</t>
+          <t>business_name? grain? + gap rows (pk phrase RETIRED 2026-09-05)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">

--- a/AIVIA_Design/L1_Code_Structure_Map_DRAFT.xlsx
+++ b/AIVIA_Design/L1_Code_Structure_Map_DRAFT.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>business_name? grain? + gap rows (pk phrase RETIRED 2026-09-05)</t>
+          <t>grain? + gap rows (business_name CUT and pk phrase RETIRED, 2026-09-05 — grain is the phrase rules' sole surviving yield)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
